--- a/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U50_P03S49_AvgUserSatisfaction_4MethodCompare.xlsx
+++ b/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U50_P03S49_AvgUserSatisfaction_4MethodCompare.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="974" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2435" uniqueCount="7">
   <si>
     <t>time_offset_from_worst_epfd_slot_s</t>
   </si>

--- a/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U50_P03S49_AvgUserSatisfaction_4MethodCompare.xlsx
+++ b/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U50_P03S49_AvgUserSatisfaction_4MethodCompare.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2435" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3409" uniqueCount="9">
   <si>
     <t>time_offset_from_worst_epfd_slot_s</t>
   </si>
@@ -34,6 +34,12 @@
   </si>
   <si>
     <t>SAPR-R</t>
+  </si>
+  <si>
+    <t>Only HBR</t>
+  </si>
+  <si>
+    <t>EABR</t>
   </si>
 </sst>
 </file>
@@ -82,9 +88,9 @@
   <dimension ref="A1:C485"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" customWidth="true"/>
-    <col min="2" max="2" width="25.88671875" customWidth="true"/>
-    <col min="3" max="3" width="18" customWidth="true"/>
+    <col min="1" max="1" width="34.140625" customWidth="true"/>
+    <col min="2" max="2" width="28" customWidth="true"/>
+    <col min="3" max="3" width="19.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2768,7 +2774,7 @@
         <v>100</v>
       </c>
       <c r="C244" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="245">
@@ -2779,7 +2785,7 @@
         <v>100</v>
       </c>
       <c r="C245" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="246">
@@ -2790,7 +2796,7 @@
         <v>100</v>
       </c>
       <c r="C246" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="247">
@@ -2801,7 +2807,7 @@
         <v>100</v>
       </c>
       <c r="C247" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="248">
@@ -2812,7 +2818,7 @@
         <v>100</v>
       </c>
       <c r="C248" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="249">
@@ -2823,7 +2829,7 @@
         <v>100</v>
       </c>
       <c r="C249" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="250">
@@ -2834,7 +2840,7 @@
         <v>100</v>
       </c>
       <c r="C250" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="251">
@@ -2845,7 +2851,7 @@
         <v>100</v>
       </c>
       <c r="C251" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="252">
@@ -2856,7 +2862,7 @@
         <v>100</v>
       </c>
       <c r="C252" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="253">
@@ -2867,7 +2873,7 @@
         <v>100</v>
       </c>
       <c r="C253" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="254">
@@ -2878,7 +2884,7 @@
         <v>100</v>
       </c>
       <c r="C254" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="255">
@@ -2889,7 +2895,7 @@
         <v>100</v>
       </c>
       <c r="C255" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="256">
@@ -2900,7 +2906,7 @@
         <v>100</v>
       </c>
       <c r="C256" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="257">
@@ -2911,7 +2917,7 @@
         <v>100</v>
       </c>
       <c r="C257" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="258">
@@ -2922,7 +2928,7 @@
         <v>100</v>
       </c>
       <c r="C258" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="259">
@@ -2933,7 +2939,7 @@
         <v>100</v>
       </c>
       <c r="C259" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="260">
@@ -2944,7 +2950,7 @@
         <v>100</v>
       </c>
       <c r="C260" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="261">
@@ -2955,7 +2961,7 @@
         <v>100</v>
       </c>
       <c r="C261" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="262">
@@ -2966,7 +2972,7 @@
         <v>100</v>
       </c>
       <c r="C262" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="263">
@@ -2977,7 +2983,7 @@
         <v>96.14380980094532</v>
       </c>
       <c r="C263" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="264">
@@ -2988,7 +2994,7 @@
         <v>96.134825240530589</v>
       </c>
       <c r="C264" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="265">
@@ -2999,7 +3005,7 @@
         <v>99.825526841397362</v>
       </c>
       <c r="C265" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="266">
@@ -3010,7 +3016,7 @@
         <v>91.818063045073231</v>
       </c>
       <c r="C266" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="267">
@@ -3021,7 +3027,7 @@
         <v>89.758194821919076</v>
       </c>
       <c r="C267" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="268">
@@ -3032,7 +3038,7 @@
         <v>94.415637947904685</v>
       </c>
       <c r="C268" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="269">
@@ -3043,7 +3049,7 @@
         <v>94.520308306298887</v>
       </c>
       <c r="C269" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="270">
@@ -3054,7 +3060,7 @@
         <v>94.618760379977047</v>
       </c>
       <c r="C270" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="271">
@@ -3065,7 +3071,7 @@
         <v>94.605607087246653</v>
       </c>
       <c r="C271" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="272">
@@ -3076,7 +3082,7 @@
         <v>96.767829150742386</v>
       </c>
       <c r="C272" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="273">
@@ -3087,7 +3093,7 @@
         <v>98.902086874306519</v>
       </c>
       <c r="C273" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="274">
@@ -3098,7 +3104,7 @@
         <v>98.562243685959245</v>
       </c>
       <c r="C274" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="275">
@@ -3109,7 +3115,7 @@
         <v>97.875491856327187</v>
       </c>
       <c r="C275" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="276">
@@ -3120,7 +3126,7 @@
         <v>97.418661573950914</v>
       </c>
       <c r="C276" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="277">
@@ -3131,7 +3137,7 @@
         <v>97.394135162600264</v>
       </c>
       <c r="C277" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="278">
@@ -3142,7 +3148,7 @@
         <v>94.243488720507557</v>
       </c>
       <c r="C278" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="279">
@@ -3153,7 +3159,7 @@
         <v>90.424093560576125</v>
       </c>
       <c r="C279" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="280">
@@ -3164,7 +3170,7 @@
         <v>89.915190607287983</v>
       </c>
       <c r="C280" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="281">
@@ -3175,7 +3181,7 @@
         <v>90.260496144212311</v>
       </c>
       <c r="C281" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="282">
@@ -3186,7 +3192,7 @@
         <v>90.034112746658465</v>
       </c>
       <c r="C282" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="283">
@@ -3197,7 +3203,7 @@
         <v>90.351848392977487</v>
       </c>
       <c r="C283" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="284">
@@ -3208,7 +3214,7 @@
         <v>87.154817964645332</v>
       </c>
       <c r="C284" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="285">
@@ -3219,7 +3225,7 @@
         <v>79.263533212674844</v>
       </c>
       <c r="C285" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="286">
@@ -3230,7 +3236,7 @@
         <v>84.929418603262533</v>
       </c>
       <c r="C286" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="287">
@@ -3241,7 +3247,7 @@
         <v>85.496712907084088</v>
       </c>
       <c r="C287" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="288">
@@ -3252,7 +3258,7 @@
         <v>90.074605686294348</v>
       </c>
       <c r="C288" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="289">
@@ -3263,7 +3269,7 @@
         <v>90.084395164911072</v>
       </c>
       <c r="C289" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="290">
@@ -3274,7 +3280,7 @@
         <v>85.326824554458881</v>
       </c>
       <c r="C290" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="291">
@@ -3285,7 +3291,7 @@
         <v>87.742566732493785</v>
       </c>
       <c r="C291" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="292">
@@ -3296,7 +3302,7 @@
         <v>84.494591038468471</v>
       </c>
       <c r="C292" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="293">
@@ -3307,7 +3313,7 @@
         <v>84.778740919869534</v>
       </c>
       <c r="C293" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="294">
@@ -3318,7 +3324,7 @@
         <v>90.181095390588268</v>
       </c>
       <c r="C294" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="295">
@@ -3329,7 +3335,7 @@
         <v>87.312809722193151</v>
       </c>
       <c r="C295" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="296">
@@ -3340,7 +3346,7 @@
         <v>87.405404115109576</v>
       </c>
       <c r="C296" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="297">
@@ -3351,7 +3357,7 @@
         <v>84.098255816567573</v>
       </c>
       <c r="C297" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="298">
@@ -3362,7 +3368,7 @@
         <v>84.752985423338956</v>
       </c>
       <c r="C298" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="299">
@@ -3373,7 +3379,7 @@
         <v>84.912678816063732</v>
       </c>
       <c r="C299" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="300">
@@ -3384,7 +3390,7 @@
         <v>81.363317112954405</v>
       </c>
       <c r="C300" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="301">
@@ -3395,7 +3401,7 @@
         <v>81.584368553489185</v>
       </c>
       <c r="C301" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="302">
@@ -3406,7 +3412,7 @@
         <v>83.148988076152349</v>
       </c>
       <c r="C302" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="303">
@@ -3417,7 +3423,7 @@
         <v>83.383578371454504</v>
       </c>
       <c r="C303" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="304">
@@ -3428,7 +3434,7 @@
         <v>82.422852479507412</v>
       </c>
       <c r="C304" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="305">
@@ -3439,7 +3445,7 @@
         <v>82.201575840529998</v>
       </c>
       <c r="C305" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="306">
@@ -3450,7 +3456,7 @@
         <v>85.948465878097707</v>
       </c>
       <c r="C306" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="307">
@@ -3461,7 +3467,7 @@
         <v>88.448950249368082</v>
       </c>
       <c r="C307" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="308">
@@ -3472,7 +3478,7 @@
         <v>87.860375008822317</v>
       </c>
       <c r="C308" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="309">
@@ -3483,7 +3489,7 @@
         <v>88.212134538479972</v>
       </c>
       <c r="C309" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="310">
@@ -3494,7 +3500,7 @@
         <v>86.568147851157079</v>
       </c>
       <c r="C310" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="311">
@@ -3505,7 +3511,7 @@
         <v>85.776385224017645</v>
       </c>
       <c r="C311" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="312">
@@ -3516,7 +3522,7 @@
         <v>90.481535214407614</v>
       </c>
       <c r="C312" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="313">
@@ -3527,7 +3533,7 @@
         <v>89.613613434007021</v>
       </c>
       <c r="C313" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="314">
@@ -3538,7 +3544,7 @@
         <v>87.57672241749502</v>
       </c>
       <c r="C314" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="315">
@@ -3549,7 +3555,7 @@
         <v>83.608316524935248</v>
       </c>
       <c r="C315" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="316">
@@ -3560,7 +3566,7 @@
         <v>83.283601960347482</v>
       </c>
       <c r="C316" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="317">
@@ -3571,7 +3577,7 @@
         <v>81.770288417693507</v>
       </c>
       <c r="C317" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="318">
@@ -3582,7 +3588,7 @@
         <v>83.514144855508661</v>
       </c>
       <c r="C318" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="319">
@@ -3593,7 +3599,7 @@
         <v>86.09139649415026</v>
       </c>
       <c r="C319" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="320">
@@ -3604,7 +3610,7 @@
         <v>83.466380202205684</v>
       </c>
       <c r="C320" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="321">
@@ -3615,7 +3621,7 @@
         <v>84.023301801493915</v>
       </c>
       <c r="C321" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="322">
@@ -3626,7 +3632,7 @@
         <v>83.847736632655625</v>
       </c>
       <c r="C322" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="323">
@@ -3637,7 +3643,7 @@
         <v>84.802141581694684</v>
       </c>
       <c r="C323" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="324">
@@ -3648,7 +3654,7 @@
         <v>86.568821344937433</v>
       </c>
       <c r="C324" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="325">
@@ -3659,7 +3665,7 @@
         <v>89.138492045773773</v>
       </c>
       <c r="C325" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="326">
@@ -3670,7 +3676,7 @@
         <v>91.822901759326612</v>
       </c>
       <c r="C326" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="327">
@@ -3681,7 +3687,7 @@
         <v>91.830605952076496</v>
       </c>
       <c r="C327" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="328">
@@ -3692,7 +3698,7 @@
         <v>90.102483180053625</v>
       </c>
       <c r="C328" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="329">
@@ -3703,7 +3709,7 @@
         <v>91.481477102549604</v>
       </c>
       <c r="C329" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="330">
@@ -3714,7 +3720,7 @@
         <v>95.693652510117957</v>
       </c>
       <c r="C330" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="331">
@@ -3725,7 +3731,7 @@
         <v>96.022411258591632</v>
       </c>
       <c r="C331" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="332">
@@ -3736,7 +3742,7 @@
         <v>96.909177326700245</v>
       </c>
       <c r="C332" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="333">
@@ -3747,7 +3753,7 @@
         <v>96.829152773742138</v>
       </c>
       <c r="C333" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="334">
@@ -3758,7 +3764,7 @@
         <v>96.832241938430826</v>
       </c>
       <c r="C334" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="335">
@@ -3769,7 +3775,7 @@
         <v>94.169088380354708</v>
       </c>
       <c r="C335" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="336">
@@ -3780,7 +3786,7 @@
         <v>94.057152333471166</v>
       </c>
       <c r="C336" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="337">
@@ -3791,7 +3797,7 @@
         <v>93.522064131618535</v>
       </c>
       <c r="C337" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="338">
@@ -3802,7 +3808,7 @@
         <v>95.18245727304739</v>
       </c>
       <c r="C338" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="339">
@@ -3813,7 +3819,7 @@
         <v>94.696380795796301</v>
       </c>
       <c r="C339" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="340">
@@ -3824,7 +3830,7 @@
         <v>92.463811709228182</v>
       </c>
       <c r="C340" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="341">
@@ -3835,7 +3841,7 @@
         <v>88.373531149148775</v>
       </c>
       <c r="C341" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="342">
@@ -3846,7 +3852,7 @@
         <v>90.362098409177605</v>
       </c>
       <c r="C342" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="343">
@@ -3857,7 +3863,7 @@
         <v>96.475154150417566</v>
       </c>
       <c r="C343" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="344">
@@ -3868,7 +3874,7 @@
         <v>96.082027850621941</v>
       </c>
       <c r="C344" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="345">
@@ -3879,7 +3885,7 @@
         <v>96.095382155207091</v>
       </c>
       <c r="C345" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="346">
@@ -3890,7 +3896,7 @@
         <v>96.107138017720629</v>
       </c>
       <c r="C346" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="347">
@@ -3901,7 +3907,7 @@
         <v>100</v>
       </c>
       <c r="C347" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="348">
@@ -3912,7 +3918,7 @@
         <v>100</v>
       </c>
       <c r="C348" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="349">
@@ -3923,7 +3929,7 @@
         <v>100</v>
       </c>
       <c r="C349" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="350">
@@ -3934,7 +3940,7 @@
         <v>99.292242753567791</v>
       </c>
       <c r="C350" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="351">
@@ -3945,7 +3951,7 @@
         <v>100</v>
       </c>
       <c r="C351" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="352">
@@ -3956,7 +3962,7 @@
         <v>100</v>
       </c>
       <c r="C352" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="353">
@@ -3967,7 +3973,7 @@
         <v>100</v>
       </c>
       <c r="C353" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="354">
@@ -3978,7 +3984,7 @@
         <v>100</v>
       </c>
       <c r="C354" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="355">
@@ -3989,7 +3995,7 @@
         <v>100</v>
       </c>
       <c r="C355" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="356">
@@ -4000,7 +4006,7 @@
         <v>100</v>
       </c>
       <c r="C356" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="357">
@@ -4011,7 +4017,7 @@
         <v>100</v>
       </c>
       <c r="C357" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="358">
@@ -4022,7 +4028,7 @@
         <v>100</v>
       </c>
       <c r="C358" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="359">
@@ -4033,7 +4039,7 @@
         <v>100</v>
       </c>
       <c r="C359" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="360">
@@ -4044,7 +4050,7 @@
         <v>100</v>
       </c>
       <c r="C360" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="361">
@@ -4055,7 +4061,7 @@
         <v>100</v>
       </c>
       <c r="C361" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="362">
@@ -4066,7 +4072,7 @@
         <v>100</v>
       </c>
       <c r="C362" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="363">
@@ -4077,7 +4083,7 @@
         <v>100</v>
       </c>
       <c r="C363" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="364">
@@ -4088,7 +4094,7 @@
         <v>100</v>
       </c>
       <c r="C364" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="365">
@@ -4099,7 +4105,7 @@
         <v>100</v>
       </c>
       <c r="C365" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="366">
@@ -4110,7 +4116,7 @@
         <v>100</v>
       </c>
       <c r="C366" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="367">
@@ -4121,7 +4127,7 @@
         <v>100</v>
       </c>
       <c r="C367" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="368">
@@ -4132,7 +4138,7 @@
         <v>100</v>
       </c>
       <c r="C368" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="369">
@@ -4143,7 +4149,7 @@
         <v>100</v>
       </c>
       <c r="C369" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="370">
@@ -4154,7 +4160,7 @@
         <v>100</v>
       </c>
       <c r="C370" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="371">
@@ -4165,7 +4171,7 @@
         <v>100</v>
       </c>
       <c r="C371" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="372">
@@ -4176,7 +4182,7 @@
         <v>100</v>
       </c>
       <c r="C372" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="373">
@@ -4187,7 +4193,7 @@
         <v>100</v>
       </c>
       <c r="C373" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="374">
@@ -4198,7 +4204,7 @@
         <v>100</v>
       </c>
       <c r="C374" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="375">
@@ -4209,7 +4215,7 @@
         <v>100</v>
       </c>
       <c r="C375" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="376">
@@ -4220,7 +4226,7 @@
         <v>100</v>
       </c>
       <c r="C376" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="377">
@@ -4231,7 +4237,7 @@
         <v>100</v>
       </c>
       <c r="C377" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="378">
@@ -4242,7 +4248,7 @@
         <v>100</v>
       </c>
       <c r="C378" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="379">
@@ -4253,7 +4259,7 @@
         <v>100</v>
       </c>
       <c r="C379" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="380">
@@ -4264,7 +4270,7 @@
         <v>100</v>
       </c>
       <c r="C380" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="381">
@@ -4275,7 +4281,7 @@
         <v>100</v>
       </c>
       <c r="C381" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="382">
@@ -4286,7 +4292,7 @@
         <v>100</v>
       </c>
       <c r="C382" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="383">
@@ -4297,7 +4303,7 @@
         <v>100</v>
       </c>
       <c r="C383" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="384">
@@ -4308,7 +4314,7 @@
         <v>99.463228105491737</v>
       </c>
       <c r="C384" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="385">
@@ -4319,7 +4325,7 @@
         <v>99.45173369725741</v>
       </c>
       <c r="C385" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="386">
@@ -4330,7 +4336,7 @@
         <v>100</v>
       </c>
       <c r="C386" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="387">
@@ -4341,7 +4347,7 @@
         <v>97.721224911735831</v>
       </c>
       <c r="C387" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="388">
@@ -4352,7 +4358,7 @@
         <v>94.913977447404349</v>
       </c>
       <c r="C388" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="389">
@@ -4363,7 +4369,7 @@
         <v>98.990231820395508</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="390">
@@ -4374,7 +4380,7 @@
         <v>99.002468604488072</v>
       </c>
       <c r="C390" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="391">
@@ -4385,7 +4391,7 @@
         <v>99.013026121344794</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="392">
@@ -4396,7 +4402,7 @@
         <v>99.00245603618464</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="393">
@@ -4407,7 +4413,7 @@
         <v>100</v>
       </c>
       <c r="C393" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="394">
@@ -4418,7 +4424,7 @@
         <v>100</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="395">
@@ -4429,7 +4435,7 @@
         <v>100</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="396">
@@ -4440,7 +4446,7 @@
         <v>100</v>
       </c>
       <c r="C396" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="397">
@@ -4451,7 +4457,7 @@
         <v>100</v>
       </c>
       <c r="C397" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="398">
@@ -4462,7 +4468,7 @@
         <v>100</v>
       </c>
       <c r="C398" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="399">
@@ -4473,7 +4479,7 @@
         <v>99.087667420505539</v>
       </c>
       <c r="C399" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="400">
@@ -4484,7 +4490,7 @@
         <v>98.372128508862687</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="401">
@@ -4495,7 +4501,7 @@
         <v>97.314039144081036</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="402">
@@ -4506,7 +4512,7 @@
         <v>99.278707564644634</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="403">
@@ -4517,7 +4523,7 @@
         <v>99.24838703016492</v>
       </c>
       <c r="C403" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="404">
@@ -4528,7 +4534,7 @@
         <v>97.635658857715129</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="405">
@@ -4539,7 +4545,7 @@
         <v>98.498378378662778</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="406">
@@ -4550,7 +4556,7 @@
         <v>92.14261746451966</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="407">
@@ -4561,7 +4567,7 @@
         <v>96.528745862863559</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="408">
@@ -4572,7 +4578,7 @@
         <v>96.76000368728414</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="409">
@@ -4583,7 +4589,7 @@
         <v>99.26471960681468</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="410">
@@ -4594,7 +4600,7 @@
         <v>99.273318196328177</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="411">
@@ -4605,7 +4611,7 @@
         <v>97.651993226543695</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="412">
@@ -4616,7 +4622,7 @@
         <v>97.844359562169899</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="413">
@@ -4627,7 +4633,7 @@
         <v>95.52832141304178</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="414">
@@ -4638,7 +4644,7 @@
         <v>96.628827610560492</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="415">
@@ -4649,7 +4655,7 @@
         <v>99.055726510070215</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="416">
@@ -4660,7 +4666,7 @@
         <v>96.473127460254403</v>
       </c>
       <c r="C416" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="417">
@@ -4671,7 +4677,7 @@
         <v>97.983820912022367</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="418">
@@ -4682,7 +4688,7 @@
         <v>95.226258829207865</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="419">
@@ -4693,7 +4699,7 @@
         <v>96.427535034430207</v>
       </c>
       <c r="C419" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="420">
@@ -4704,7 +4710,7 @@
         <v>97.588868102811205</v>
       </c>
       <c r="C420" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="421">
@@ -4715,7 +4721,7 @@
         <v>95.417719930966328</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="422">
@@ -4726,7 +4732,7 @@
         <v>95.724839865061199</v>
       </c>
       <c r="C422" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="423">
@@ -4737,7 +4743,7 @@
         <v>98.010070035693957</v>
       </c>
       <c r="C423" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="424">
@@ -4748,7 +4754,7 @@
         <v>97.236705034284569</v>
       </c>
       <c r="C424" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="425">
@@ -4759,7 +4765,7 @@
         <v>95.911305935317884</v>
       </c>
       <c r="C425" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="426">
@@ -4770,7 +4776,7 @@
         <v>96.242073142295595</v>
       </c>
       <c r="C426" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="427">
@@ -4781,7 +4787,7 @@
         <v>98.543679058331804</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="428">
@@ -4792,7 +4798,7 @@
         <v>99.07054064370179</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="429">
@@ -4803,7 +4809,7 @@
         <v>98.594935259991303</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="430">
@@ -4814,7 +4820,7 @@
         <v>98.658298653893155</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="431">
@@ -4825,7 +4831,7 @@
         <v>97.309150584760758</v>
       </c>
       <c r="C431" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="432">
@@ -4836,7 +4842,7 @@
         <v>98.123416999397648</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="433">
@@ -4847,7 +4853,7 @@
         <v>99.631835575149992</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="434">
@@ -4858,7 +4864,7 @@
         <v>97.264624894792206</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="435">
@@ -4869,7 +4875,7 @@
         <v>97.173340942060534</v>
       </c>
       <c r="C435" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="436">
@@ -4880,7 +4886,7 @@
         <v>93.681738883990676</v>
       </c>
       <c r="C436" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="437">
@@ -4891,7 +4897,7 @@
         <v>95.768967514163563</v>
       </c>
       <c r="C437" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="438">
@@ -4902,7 +4908,7 @@
         <v>94.773080127075005</v>
       </c>
       <c r="C438" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="439">
@@ -4913,7 +4919,7 @@
         <v>97.069928564801799</v>
       </c>
       <c r="C439" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="440">
@@ -4924,7 +4930,7 @@
         <v>97.957060469264036</v>
       </c>
       <c r="C440" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="441">
@@ -4935,7 +4941,7 @@
         <v>95.741292172002787</v>
       </c>
       <c r="C441" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="442">
@@ -4946,7 +4952,7 @@
         <v>96.147528286734143</v>
       </c>
       <c r="C442" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="443">
@@ -4957,7 +4963,7 @@
         <v>97.74001849701277</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="444">
@@ -4968,7 +4974,7 @@
         <v>95.814467569765114</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="445">
@@ -4979,7 +4985,7 @@
         <v>96.146109777534377</v>
       </c>
       <c r="C445" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="446">
@@ -4990,7 +4996,7 @@
         <v>96.330807601292719</v>
       </c>
       <c r="C446" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="447">
@@ -5001,7 +5007,7 @@
         <v>99.056023380856487</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="448">
@@ -5012,7 +5018,7 @@
         <v>99.06265244199443</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="449">
@@ -5023,7 +5029,7 @@
         <v>98.971155839882755</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="450">
@@ -5034,7 +5040,7 @@
         <v>97.974671530888912</v>
       </c>
       <c r="C450" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="451">
@@ -5045,7 +5051,7 @@
         <v>99.965331096636959</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="452">
@@ -5056,7 +5062,7 @@
         <v>100</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="453">
@@ -5067,7 +5073,7 @@
         <v>100</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="454">
@@ -5078,7 +5084,7 @@
         <v>100</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="455">
@@ -5089,7 +5095,7 @@
         <v>100</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="456">
@@ -5100,7 +5106,7 @@
         <v>98.020531432926148</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="457">
@@ -5111,7 +5117,7 @@
         <v>97.985245302687588</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="458">
@@ -5122,7 +5128,7 @@
         <v>98.422672344262978</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="459">
@@ -5133,7 +5139,7 @@
         <v>98.453765337595499</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="460">
@@ -5144,7 +5150,7 @@
         <v>98.458178139996519</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="461">
@@ -5155,7 +5161,7 @@
         <v>97.011304723310914</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="462">
@@ -5166,7 +5172,7 @@
         <v>95.778125750469613</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="463">
@@ -5177,7 +5183,7 @@
         <v>96.03742713505433</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="464">
@@ -5188,7 +5194,7 @@
         <v>99.143782132782803</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="465">
@@ -5199,7 +5205,7 @@
         <v>99.14791179866252</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="466">
@@ -5210,7 +5216,7 @@
         <v>99.151618010871786</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="467">
@@ -5221,7 +5227,7 @@
         <v>99.154895458731303</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="468">
@@ -5232,7 +5238,7 @@
         <v>100</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="469">
@@ -5243,7 +5249,7 @@
         <v>100</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="470">
@@ -5254,7 +5260,7 @@
         <v>100</v>
       </c>
       <c r="C470" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="471">
@@ -5265,7 +5271,7 @@
         <v>100</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="472">
@@ -5276,7 +5282,7 @@
         <v>100</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="473">
@@ -5287,7 +5293,7 @@
         <v>100</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="474">
@@ -5298,7 +5304,7 @@
         <v>100</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="475">
@@ -5309,7 +5315,7 @@
         <v>100</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="476">
@@ -5320,7 +5326,7 @@
         <v>100</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="477">
@@ -5331,7 +5337,7 @@
         <v>100</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="478">
@@ -5342,7 +5348,7 @@
         <v>100</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="479">
@@ -5353,7 +5359,7 @@
         <v>100</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="480">
@@ -5364,7 +5370,7 @@
         <v>100</v>
       </c>
       <c r="C480" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="481">
@@ -5375,7 +5381,7 @@
         <v>100</v>
       </c>
       <c r="C481" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="482">
@@ -5386,7 +5392,7 @@
         <v>100</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="483">
@@ -5397,7 +5403,7 @@
         <v>100</v>
       </c>
       <c r="C483" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="484">
@@ -5408,7 +5414,7 @@
         <v>100</v>
       </c>
       <c r="C484" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="485">
@@ -5419,7 +5425,7 @@
         <v>100</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U50_P03S49_AvgUserSatisfaction_4MethodCompare.xlsx
+++ b/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U50_P03S49_AvgUserSatisfaction_4MethodCompare.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3409" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3896" uniqueCount="10">
   <si>
     <t>time_offset_from_worst_epfd_slot_s</t>
   </si>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t>EABR</t>
+  </si>
+  <si>
+    <t>PC + Tilt</t>
   </si>
 </sst>
 </file>
@@ -88,9 +91,9 @@
   <dimension ref="A1:C485"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.140625" customWidth="true"/>
-    <col min="2" max="2" width="28" customWidth="true"/>
-    <col min="3" max="3" width="19.7109375" customWidth="true"/>
+    <col min="1" max="1" width="31.6640625" customWidth="true"/>
+    <col min="2" max="2" width="25.88671875" customWidth="true"/>
+    <col min="3" max="3" width="18" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1443,7 +1446,7 @@
         <v>100</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124">
@@ -1454,7 +1457,7 @@
         <v>100</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125">
@@ -1465,7 +1468,7 @@
         <v>100</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126">
@@ -1476,7 +1479,7 @@
         <v>100</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="127">
@@ -1487,7 +1490,7 @@
         <v>100</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="128">
@@ -1498,7 +1501,7 @@
         <v>100</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="129">
@@ -1509,7 +1512,7 @@
         <v>100</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130">
@@ -1520,7 +1523,7 @@
         <v>100</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131">
@@ -1531,7 +1534,7 @@
         <v>100</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132">
@@ -1542,7 +1545,7 @@
         <v>100</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133">
@@ -1553,7 +1556,7 @@
         <v>100</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134">
@@ -1564,7 +1567,7 @@
         <v>100</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135">
@@ -1575,7 +1578,7 @@
         <v>100</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136">
@@ -1586,7 +1589,7 @@
         <v>100</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="137">
@@ -1597,7 +1600,7 @@
         <v>100</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138">
@@ -1608,7 +1611,7 @@
         <v>100</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139">
@@ -1619,7 +1622,7 @@
         <v>100</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140">
@@ -1630,7 +1633,7 @@
         <v>100</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141">
@@ -1641,7 +1644,7 @@
         <v>100</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142">
@@ -1652,7 +1655,7 @@
         <v>100</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143">
@@ -1663,7 +1666,7 @@
         <v>100</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144">
@@ -1674,7 +1677,7 @@
         <v>90.400011425804237</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145">
@@ -1685,7 +1688,7 @@
         <v>90.40000599800257</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146">
@@ -1696,7 +1699,7 @@
         <v>90.204093054380621</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147">
@@ -1707,7 +1710,7 @@
         <v>80.000020862417102</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148">
@@ -1718,7 +1721,7 @@
         <v>80.408181985910787</v>
       </c>
       <c r="C148" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="149">
@@ -1729,7 +1732,7 @@
         <v>84.000008379072625</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="150">
@@ -1740,7 +1743,7 @@
         <v>76.000030918080384</v>
       </c>
       <c r="C150" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="151">
@@ -1751,7 +1754,7 @@
         <v>75.510235337562122</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="152">
@@ -1762,7 +1765,7 @@
         <v>73.877575407758513</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="153">
@@ -1773,7 +1776,7 @@
         <v>74.40001809322149</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154">
@@ -1784,7 +1787,7 @@
         <v>68.000034457941382</v>
       </c>
       <c r="C154" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="155">
@@ -1795,7 +1798,7 @@
         <v>64.800034392705996</v>
       </c>
       <c r="C155" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="156">
@@ -1806,7 +1809,7 @@
         <v>64.800027642352191</v>
       </c>
       <c r="C156" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157">
@@ -1817,7 +1820,7 @@
         <v>55.200047345352473</v>
       </c>
       <c r="C157" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158">
@@ -1828,7 +1831,7 @@
         <v>55.20004750161899</v>
       </c>
       <c r="C158" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="159">
@@ -1839,7 +1842,7 @@
         <v>61.600039573927631</v>
       </c>
       <c r="C159" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="160">
@@ -1850,7 +1853,7 @@
         <v>61.600025646289971</v>
       </c>
       <c r="C160" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161">
@@ -1861,7 +1864,7 @@
         <v>52.653115133792603</v>
       </c>
       <c r="C161" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="162">
@@ -1872,7 +1875,7 @@
         <v>50.400052538484928</v>
       </c>
       <c r="C162" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="163">
@@ -1883,7 +1886,7 @@
         <v>53.600040083533216</v>
       </c>
       <c r="C163" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="164">
@@ -1894,7 +1897,7 @@
         <v>47.755146508025135</v>
       </c>
       <c r="C164" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="165">
@@ -1905,7 +1908,7 @@
         <v>51.020458242009269</v>
       </c>
       <c r="C165" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166">
@@ -1916,7 +1919,7 @@
         <v>39.5919083367532</v>
       </c>
       <c r="C166" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167">
@@ -1927,7 +1930,7 @@
         <v>42.400045713531298</v>
       </c>
       <c r="C167" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168">
@@ -1938,7 +1941,7 @@
         <v>42.400072888958121</v>
       </c>
       <c r="C168" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="169">
@@ -1949,7 +1952,7 @@
         <v>42.400054063746566</v>
       </c>
       <c r="C169" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="170">
@@ -1960,7 +1963,7 @@
         <v>41.224528010104748</v>
       </c>
       <c r="C170" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="171">
@@ -1971,7 +1974,7 @@
         <v>34.400058504867864</v>
       </c>
       <c r="C171" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="172">
@@ -1982,7 +1985,7 @@
         <v>31.200073269855306</v>
       </c>
       <c r="C172" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="173">
@@ -1993,7 +1996,7 @@
         <v>31.200072227367709</v>
       </c>
       <c r="C173" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="174">
@@ -2004,7 +2007,7 @@
         <v>31.200055043530806</v>
       </c>
       <c r="C174" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="175">
@@ -2015,7 +2018,7 @@
         <v>29.600080755955226</v>
       </c>
       <c r="C175" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="176">
@@ -2026,7 +2029,7 @@
         <v>31.200060836497883</v>
       </c>
       <c r="C176" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="177">
@@ -2037,7 +2040,7 @@
         <v>36.000061466011964</v>
       </c>
       <c r="C177" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178">
@@ -2048,7 +2051,7 @@
         <v>31.200062252943344</v>
       </c>
       <c r="C178" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="179">
@@ -2059,7 +2062,7 @@
         <v>33.061284009565476</v>
       </c>
       <c r="C179" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="180">
@@ -2070,7 +2073,7 @@
         <v>29.600070564131407</v>
       </c>
       <c r="C180" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="181">
@@ -2081,7 +2084,7 @@
         <v>21.600118314464385</v>
       </c>
       <c r="C181" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="182">
@@ -2092,7 +2095,7 @@
         <v>29.796000207160528</v>
       </c>
       <c r="C182" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="183">
@@ -2103,7 +2106,7 @@
         <v>28.163329843637001</v>
       </c>
       <c r="C183" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="184">
@@ -2114,7 +2117,7 @@
         <v>24.89805834994204</v>
       </c>
       <c r="C184" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="185">
@@ -2125,7 +2128,7 @@
         <v>26.666755109114426</v>
       </c>
       <c r="C185" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="186">
@@ -2136,7 +2139,7 @@
         <v>31.200053165799851</v>
       </c>
       <c r="C186" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="187">
@@ -2147,7 +2150,7 @@
         <v>31.200047404565822</v>
       </c>
       <c r="C187" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="188">
@@ -2158,7 +2161,7 @@
         <v>31.200061333423061</v>
       </c>
       <c r="C188" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="189">
@@ -2169,7 +2172,7 @@
         <v>33.061292557764823</v>
       </c>
       <c r="C189" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="190">
@@ -2180,7 +2183,7 @@
         <v>29.600068219156654</v>
       </c>
       <c r="C190" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="191">
@@ -2191,7 +2194,7 @@
         <v>32.800049956262008</v>
       </c>
       <c r="C191" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="192">
@@ -2202,7 +2205,7 @@
         <v>31.200059421188591</v>
       </c>
       <c r="C192" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="193">
@@ -2213,7 +2216,7 @@
         <v>31.200075179605236</v>
       </c>
       <c r="C193" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="194">
@@ -2224,7 +2227,7 @@
         <v>34.400055766956022</v>
       </c>
       <c r="C194" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="195">
@@ -2235,7 +2238,7 @@
         <v>34.400069692903465</v>
       </c>
       <c r="C195" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="196">
@@ -2246,7 +2249,7 @@
         <v>42.857193486940339</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="197">
@@ -2257,7 +2260,7 @@
         <v>37.959254114437783</v>
       </c>
       <c r="C197" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="198">
@@ -2268,7 +2271,7 @@
         <v>39.200069786437687</v>
       </c>
       <c r="C198" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="199">
@@ -2279,7 +2282,7 @@
         <v>44.000064098117242</v>
       </c>
       <c r="C199" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="200">
@@ -2290,7 +2293,7 @@
         <v>50.400048064618197</v>
       </c>
       <c r="C200" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="201">
@@ -2301,7 +2304,7 @@
         <v>49.387810823271671</v>
       </c>
       <c r="C201" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="202">
@@ -2312,7 +2315,7 @@
         <v>53.333377119922844</v>
       </c>
       <c r="C202" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="203">
@@ -2323,7 +2326,7 @@
         <v>51.020448345139883</v>
       </c>
       <c r="C203" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="204">
@@ -2334,7 +2337,7 @@
         <v>53.600055149814565</v>
       </c>
       <c r="C204" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="205">
@@ -2345,7 +2348,7 @@
         <v>61.600022414969814</v>
       </c>
       <c r="C205" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="206">
@@ -2356,7 +2359,7 @@
         <v>61.600037565031393</v>
       </c>
       <c r="C206" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="207">
@@ -2367,7 +2370,7 @@
         <v>55.200051185864538</v>
       </c>
       <c r="C207" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="208">
@@ -2378,7 +2381,7 @@
         <v>61.600034402316929</v>
       </c>
       <c r="C208" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="209">
@@ -2389,7 +2392,7 @@
         <v>61.600054601645397</v>
       </c>
       <c r="C209" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="210">
@@ -2400,7 +2403,7 @@
         <v>66.400031471863812</v>
       </c>
       <c r="C210" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="211">
@@ -2411,7 +2414,7 @@
         <v>68.000037304367453</v>
       </c>
       <c r="C211" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="212">
@@ -2422,7 +2425,7 @@
         <v>66.400048347507578</v>
       </c>
       <c r="C212" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="213">
@@ -2433,7 +2436,7 @@
         <v>72.800028375067953</v>
       </c>
       <c r="C213" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="214">
@@ -2444,7 +2447,7 @@
         <v>72.244931887594618</v>
       </c>
       <c r="C214" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="215">
@@ -2455,7 +2458,7 @@
         <v>75.000018921042383</v>
       </c>
       <c r="C215" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="216">
@@ -2466,7 +2469,7 @@
         <v>80.800020126796028</v>
       </c>
       <c r="C216" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="217">
@@ -2477,7 +2480,7 @@
         <v>80.800026199997575</v>
       </c>
       <c r="C217" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="218">
@@ -2488,7 +2491,7 @@
         <v>80.800024753736679</v>
       </c>
       <c r="C218" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="219">
@@ -2499,7 +2502,7 @@
         <v>80.408187978465691</v>
       </c>
       <c r="C219" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="220">
@@ -2510,7 +2513,7 @@
         <v>90.204094646746384</v>
       </c>
       <c r="C220" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="221">
@@ -2521,7 +2524,7 @@
         <v>90.40001076956014</v>
       </c>
       <c r="C221" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="222">
@@ -2532,7 +2535,7 @@
         <v>92.000011087393119</v>
       </c>
       <c r="C222" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="223">
@@ -2543,7 +2546,7 @@
         <v>100</v>
       </c>
       <c r="C223" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="224">
@@ -2554,7 +2557,7 @@
         <v>100</v>
       </c>
       <c r="C224" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="225">
@@ -2565,7 +2568,7 @@
         <v>100</v>
       </c>
       <c r="C225" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="226">
@@ -2576,7 +2579,7 @@
         <v>100</v>
       </c>
       <c r="C226" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="227">
@@ -2587,7 +2590,7 @@
         <v>100</v>
       </c>
       <c r="C227" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="228">
@@ -2598,7 +2601,7 @@
         <v>100</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="229">
@@ -2609,7 +2612,7 @@
         <v>100</v>
       </c>
       <c r="C229" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="230">
@@ -2620,7 +2623,7 @@
         <v>100</v>
       </c>
       <c r="C230" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="231">
@@ -2631,7 +2634,7 @@
         <v>100</v>
       </c>
       <c r="C231" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="232">
@@ -2642,7 +2645,7 @@
         <v>100</v>
       </c>
       <c r="C232" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="233">
@@ -2653,7 +2656,7 @@
         <v>100</v>
       </c>
       <c r="C233" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="234">
@@ -2664,7 +2667,7 @@
         <v>100</v>
       </c>
       <c r="C234" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="235">
@@ -2675,7 +2678,7 @@
         <v>100</v>
       </c>
       <c r="C235" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="236">
@@ -2686,7 +2689,7 @@
         <v>100</v>
       </c>
       <c r="C236" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="237">
@@ -2697,7 +2700,7 @@
         <v>100</v>
       </c>
       <c r="C237" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="238">
@@ -2708,7 +2711,7 @@
         <v>100</v>
       </c>
       <c r="C238" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="239">
@@ -2719,7 +2722,7 @@
         <v>100</v>
       </c>
       <c r="C239" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="240">
@@ -2730,7 +2733,7 @@
         <v>100</v>
       </c>
       <c r="C240" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="241">
@@ -2741,7 +2744,7 @@
         <v>100</v>
       </c>
       <c r="C241" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="242">
@@ -2752,7 +2755,7 @@
         <v>100</v>
       </c>
       <c r="C242" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="243">
@@ -2763,7 +2766,7 @@
         <v>100</v>
       </c>
       <c r="C243" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="244">
